--- a/backtest/results_hk/七星港股版_实盘交易记录.xlsx
+++ b/backtest/results_hk/七星港股版_实盘交易记录.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4340,10 +4340,8 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>02038</t>
-        </is>
+      <c r="B116" t="n">
+        <v>2038</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4367,6 +4365,1878 @@
       <c r="H116" t="inlineStr">
         <is>
           <t>持久化交易: 动量排名5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F117" t="n">
+        <v>100</v>
+      </c>
+      <c r="G117" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>141</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G118" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>981</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>522</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G120" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F121" t="n">
+        <v>10400</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1238</v>
+      </c>
+      <c r="F122" t="n">
+        <v>100</v>
+      </c>
+      <c r="G122" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>华虹半导体</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G123" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>981</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G124" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名3</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>522</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ASMPT</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名4</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>富智康集团</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="F126" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>1238</v>
+      </c>
+      <c r="F127" t="n">
+        <v>100</v>
+      </c>
+      <c r="G127" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G128" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>981</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="F129" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>522</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="F131" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>1196</v>
+      </c>
+      <c r="F132" t="n">
+        <v>100</v>
+      </c>
+      <c r="G132" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>华虹半导体</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G133" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>981</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="F134" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名3</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>522</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ASMPT</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>富智康集团</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="F136" t="n">
+        <v>10700</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>1196</v>
+      </c>
+      <c r="F137" t="n">
+        <v>100</v>
+      </c>
+      <c r="G137" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G138" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>981</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="F139" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G139" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>522</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G140" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="F141" t="n">
+        <v>10700</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F142" t="n">
+        <v>100</v>
+      </c>
+      <c r="G142" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>华虹半导体</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G143" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>981</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>67.45</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名3</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>522</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ASMPT</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>168.4</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G145" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名4</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>富智康集团</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="F146" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名5</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F147" t="n">
+        <v>100</v>
+      </c>
+      <c r="G147" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G148" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>981</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>67.45</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G149" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>522</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>168.4</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="F151" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>持久化交易: 不在今日目标中</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1275</v>
+      </c>
+      <c r="F152" t="n">
+        <v>100</v>
+      </c>
+      <c r="G152" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>华虹半导体</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G153" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>981</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F154" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名3</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>522</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ASMPT</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>175.6</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G155" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名4</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>富智康集团</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F156" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名5</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1275</v>
+      </c>
+      <c r="F157" t="n">
+        <v>100</v>
+      </c>
+      <c r="G157" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>华虹半导体</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G158" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>981</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F159" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G159" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>522</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ASMPT</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>175.6</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G160" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>富智康集团</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F161" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>1058</v>
+      </c>
+      <c r="F162" t="n">
+        <v>100</v>
+      </c>
+      <c r="G162" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>华虹半导体</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G163" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>981</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>75.65000000000001</v>
+      </c>
+      <c r="F164" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G164" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名3</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>522</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ASMPT</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>175</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G165" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名4</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>富智康集团</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="F166" t="n">
+        <v>11100</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>持久化交易: 动量排名5</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>1058</v>
+      </c>
+      <c r="F167" t="n">
+        <v>100</v>
+      </c>
+      <c r="G167" t="n">
+        <v>998.7968351089983</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>华虹半导体</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G168" t="n">
+        <v>15.49291781002961</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>981</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>75.65000000000001</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G169" t="n">
+        <v>4.320341775765378</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>522</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ASMPT</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>175</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G170" t="n">
+        <v>3.266263650219345</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>富智康集团</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="F171" t="n">
+        <v>11100</v>
+      </c>
+      <c r="G171" t="n">
+        <v>2.193924991215976</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>HSTECH恐慌期强制清仓</t>
         </is>
       </c>
     </row>
